--- a/healthcare_surveys/041_healthcare_provider_review_form--healthcare_surveys.xlsx
+++ b/healthcare_surveys/041_healthcare_provider_review_form--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -857,8 +857,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -886,12 +886,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_0,_'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 0, 'label': 'Excellent', 'value': 'excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_0,_'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 0, 'label': 'Excellent', 'value': 'excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_0,_'label':_'early',_'value':_'early'}</t>
+          <t>early</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 0, 'label': 'Early', 'value': 'early'}</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'on_time',_'value':_'on_time'}</t>
+          <t>on_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'On time', 'value': 'on_time'}</t>
+          <t>On time</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'late',_'value':_'late'}</t>
+          <t>late</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Late', 'value': 'late'}</t>
+          <t>Late</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_0,_'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 0, 'label': 'Excellent', 'value': 'excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_0,_'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 0, 'label': 'Excellent', 'value': 'excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_0,_'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 0, 'label': 'Excellent', 'value': 'excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_0,_'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 0, 'label': 'Excellent', 'value': 'excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_0,_'label':_'submit',_'value':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 0, 'label': 'Submit', 'value': 'submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_0,_'label':_'cancel',_'value':_'cancel'}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 0, 'label': 'Cancel', 'value': 'cancel'}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
